--- a/data/hex_xlsx/SSH1V.HE.xlsx
+++ b/data/hex_xlsx/SSH1V.HE.xlsx
@@ -11791,7 +11791,10 @@
         <f t="shared" si="1"/>
         <v>1.29</v>
       </c>
-      <c r="T65" s="16"/>
+      <c r="T65" s="16">
+        <f>T67+T70+T78+T81</f>
+        <v>1.17</v>
+      </c>
       <c r="U65" s="16">
         <f t="shared" ref="U65:V65" si="2">SUM(U66)</f>
         <v>0.77</v>
